--- a/Doble Rendija/toma_de_datos_doblerendija.xlsx
+++ b/Doble Rendija/toma_de_datos_doblerendija.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniandes-my.sharepoint.com/personal/av_bustos_uniandes_edu_co/Documents/Escritorio/Lab-Intermedio/Doble Rendija/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="783" documentId="14_{3CAABADE-BE41-41EC-B857-87693E98965B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD80454B-751C-41C0-B527-9764D9E9E673}"/>
+  <xr:revisionPtr revIDLastSave="796" documentId="14_{3CAABADE-BE41-41EC-B857-87693E98965B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52330DC6-F414-4031-BE4E-99F253892F29}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" activeTab="1" xr2:uid="{AACBDC3B-27A3-4B05-A44B-C0E5AE496FEC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" activeTab="2" xr2:uid="{AACBDC3B-27A3-4B05-A44B-C0E5AE496FEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Doble Rendija" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
   <si>
     <t>Voltaje (mV)</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>Conteos - Pulsos</t>
+  </si>
+  <si>
+    <t>Desviación</t>
   </si>
 </sst>
 </file>
@@ -6529,6 +6532,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
@@ -6846,14 +6853,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{096A8019-8937-44FB-A2CF-07220879DB32}">
-  <dimension ref="A1:D193"/>
+  <dimension ref="A1:M193"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" customWidth="1"/>
     <col min="3" max="3" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -6861,7 +6868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2">
         <f>C2</f>
         <v>0</v>
@@ -6874,7 +6881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>A2+5</f>
         <v>5</v>
@@ -6887,7 +6894,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4">
         <f t="shared" ref="A4:A67" si="0">A3+5</f>
         <v>10</v>
@@ -6896,11 +6903,15 @@
         <v>14.1</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="A4:C60" si="1">C3+50</f>
+        <f t="shared" ref="C4:C60" si="1">C3+50</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="M4">
+        <f>MAX(B2:B193)</f>
+        <v>165.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -6913,7 +6924,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -6926,7 +6937,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -6939,7 +6950,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -6952,7 +6963,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -6965,7 +6976,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -6978,7 +6989,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -6991,7 +7002,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -7004,7 +7015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -7017,7 +7028,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -7030,7 +7041,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -7043,7 +7054,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>70</v>
@@ -9160,13 +9171,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D13AFB9-1607-4697-B3E3-8FC1BB0FDCCC}">
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:N100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9174,7 +9185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
@@ -9186,7 +9197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>20</v>
       </c>
@@ -9197,8 +9208,12 @@
         <f t="shared" ref="C3:C66" si="0">MOD(A3,50)</f>
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="N3">
+        <f>MAX(C1:C192)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>40</v>
       </c>
@@ -9210,7 +9225,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>A4+20</f>
         <v>60</v>
@@ -9223,7 +9238,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" ref="A6:A69" si="1">A5+20</f>
         <v>80</v>
@@ -9236,7 +9251,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -9249,7 +9264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="1"/>
         <v>120</v>
@@ -9262,7 +9277,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="1"/>
         <v>140</v>
@@ -9275,7 +9290,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="1"/>
         <v>160</v>
@@ -9288,7 +9303,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="1"/>
         <v>180</v>
@@ -9301,7 +9316,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="1"/>
         <v>200</v>
@@ -9314,7 +9329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="1"/>
         <v>220</v>
@@ -9327,7 +9342,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="1"/>
         <v>240</v>
@@ -9340,7 +9355,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15">
         <f t="shared" si="1"/>
         <v>260</v>
@@ -9353,7 +9368,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16">
         <f t="shared" si="1"/>
         <v>280</v>
@@ -10322,21 +10337,25 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1650FF8-A8FB-43DC-A54A-40C971D23709}">
-  <dimension ref="A1:E174"/>
+  <dimension ref="A1:O174"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17.85546875" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>3</v>
       </c>
       <c r="B1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
@@ -10353,8 +10372,12 @@
       <c r="E2">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2">
+        <f>_xlfn.STDEV.S(C2:E2)</f>
+        <v>3.7859388972001797</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>A2+5</f>
         <v>5</v>
@@ -10372,10 +10395,18 @@
       <c r="E3">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3">
+        <f t="shared" ref="F3:F66" si="1">_xlfn.STDEV.S(C3:E3)</f>
+        <v>1.5275252316519468</v>
+      </c>
+      <c r="O3">
+        <f>MAX(D1:D192)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
-        <f t="shared" ref="A4:A67" si="1">A3+5</f>
+        <f t="shared" ref="A4:A67" si="2">A3+5</f>
         <v>10</v>
       </c>
       <c r="B4">
@@ -10391,10 +10422,14 @@
       <c r="E4">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4">
+        <f t="shared" si="1"/>
+        <v>5.5075705472861003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="B5">
@@ -10410,10 +10445,14 @@
       <c r="E5">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="B6">
@@ -10429,10 +10468,14 @@
       <c r="E6">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>5.5075705472861003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="B7">
@@ -10448,10 +10491,14 @@
       <c r="E7">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7">
+        <f t="shared" si="1"/>
+        <v>2.0816659994661282</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
       <c r="B8">
@@ -10467,10 +10514,14 @@
       <c r="E8">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8">
+        <f t="shared" si="1"/>
+        <v>3.0550504633038948</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>35</v>
       </c>
       <c r="B9">
@@ -10486,10 +10537,14 @@
       <c r="E9">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9">
+        <f t="shared" si="1"/>
+        <v>1.5275252316519468</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="B10">
@@ -10505,10 +10560,14 @@
       <c r="E10">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10">
+        <f t="shared" si="1"/>
+        <v>1.5275252316519499</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>45</v>
       </c>
       <c r="B11">
@@ -10524,10 +10583,14 @@
       <c r="E11">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11">
+        <f t="shared" si="1"/>
+        <v>2.6457513110645907</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
       <c r="B12">
@@ -10543,10 +10606,14 @@
       <c r="E12">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12">
+        <f t="shared" si="1"/>
+        <v>2.0816659994661348</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>55</v>
       </c>
       <c r="B13">
@@ -10562,10 +10629,14 @@
       <c r="E13">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>60</v>
       </c>
       <c r="B14">
@@ -10581,10 +10652,14 @@
       <c r="E14">
         <v>16</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14">
+        <f t="shared" si="1"/>
+        <v>3.6055512754639891</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>65</v>
       </c>
       <c r="B15">
@@ -10600,10 +10675,14 @@
       <c r="E15">
         <v>9</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15">
+        <f t="shared" si="1"/>
+        <v>2.0816659994661348</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
       <c r="B16">
@@ -10619,10 +10698,14 @@
       <c r="E16">
         <v>9</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16">
+        <f t="shared" si="1"/>
+        <v>2.5166114784235849</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>75</v>
       </c>
       <c r="B17">
@@ -10638,10 +10721,14 @@
       <c r="E17">
         <v>9</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17">
+        <f t="shared" si="1"/>
+        <v>2.6457513110645907</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>80</v>
       </c>
       <c r="B18">
@@ -10657,10 +10744,14 @@
       <c r="E18">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18">
+        <f t="shared" si="1"/>
+        <v>1.5275252316519499</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>85</v>
       </c>
       <c r="B19">
@@ -10676,10 +10767,14 @@
       <c r="E19">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19">
+        <f t="shared" si="1"/>
+        <v>6.4291005073286351</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>90</v>
       </c>
       <c r="B20">
@@ -10695,10 +10790,14 @@
       <c r="E20">
         <v>14</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95</v>
       </c>
       <c r="B21">
@@ -10714,10 +10813,14 @@
       <c r="E21">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21">
+        <f t="shared" si="1"/>
+        <v>3.5118845842842474</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="B22">
@@ -10733,10 +10836,14 @@
       <c r="E22">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22">
+        <f t="shared" si="1"/>
+        <v>3.0550504633038926</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>105</v>
       </c>
       <c r="B23">
@@ -10752,10 +10859,14 @@
       <c r="E23">
         <v>12</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23">
+        <f t="shared" si="1"/>
+        <v>2.5166114784235796</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>110</v>
       </c>
       <c r="B24">
@@ -10771,10 +10882,14 @@
       <c r="E24">
         <v>17</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24">
+        <f t="shared" si="1"/>
+        <v>4.0414518843273814</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>115</v>
       </c>
       <c r="B25">
@@ -10790,10 +10905,14 @@
       <c r="E25">
         <v>13</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>120</v>
       </c>
       <c r="B26">
@@ -10809,10 +10928,14 @@
       <c r="E26">
         <v>16</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>125</v>
       </c>
       <c r="B27">
@@ -10828,10 +10951,14 @@
       <c r="E27">
         <v>15</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F27">
+        <f t="shared" si="1"/>
+        <v>4.5092497528228987</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>130</v>
       </c>
       <c r="B28">
@@ -10847,10 +10974,14 @@
       <c r="E28">
         <v>23</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>135</v>
       </c>
       <c r="B29">
@@ -10866,10 +10997,14 @@
       <c r="E29">
         <v>17</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29">
+        <f t="shared" si="1"/>
+        <v>1.5275252316519465</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>140</v>
       </c>
       <c r="B30">
@@ -10885,10 +11020,14 @@
       <c r="E30">
         <v>20</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30">
+        <f t="shared" si="1"/>
+        <v>1.5275252316519465</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>145</v>
       </c>
       <c r="B31">
@@ -10904,10 +11043,14 @@
       <c r="E31">
         <v>18</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F31">
+        <f t="shared" si="1"/>
+        <v>1.5275252316519465</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>150</v>
       </c>
       <c r="B32">
@@ -10923,10 +11066,14 @@
       <c r="E32">
         <v>14</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F32">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>155</v>
       </c>
       <c r="B33">
@@ -10942,10 +11089,14 @@
       <c r="E33">
         <v>19</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>160</v>
       </c>
       <c r="B34">
@@ -10961,10 +11112,14 @@
       <c r="E34">
         <v>14</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F34">
+        <f t="shared" si="1"/>
+        <v>4.5092497528228987</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>165</v>
       </c>
       <c r="B35">
@@ -10980,10 +11135,14 @@
       <c r="E35">
         <v>22</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>170</v>
       </c>
       <c r="B36">
@@ -10999,10 +11158,14 @@
       <c r="E36">
         <v>29</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F36">
+        <f t="shared" si="1"/>
+        <v>3.0550504633038935</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>175</v>
       </c>
       <c r="B37">
@@ -11018,10 +11181,14 @@
       <c r="E37">
         <v>28</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F37">
+        <f t="shared" si="1"/>
+        <v>3.2145502536643242</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>180</v>
       </c>
       <c r="B38">
@@ -11037,10 +11204,14 @@
       <c r="E38">
         <v>31</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F38">
+        <f t="shared" si="1"/>
+        <v>1.5275252316519465</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>185</v>
       </c>
       <c r="B39">
@@ -11056,10 +11227,14 @@
       <c r="E39">
         <v>29</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F39">
+        <f t="shared" si="1"/>
+        <v>2.6457513110645907</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="B40">
@@ -11075,10 +11250,14 @@
       <c r="E40">
         <v>40</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F40">
+        <f t="shared" si="1"/>
+        <v>2.6457513110645907</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>195</v>
       </c>
       <c r="B41">
@@ -11094,10 +11273,14 @@
       <c r="E41">
         <v>41</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F41">
+        <f t="shared" si="1"/>
+        <v>2.5166114784235831</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200</v>
       </c>
       <c r="B42">
@@ -11113,10 +11296,14 @@
       <c r="E42">
         <v>32</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F42">
+        <f t="shared" si="1"/>
+        <v>4.5825756949558398</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>205</v>
       </c>
       <c r="B43">
@@ -11132,10 +11319,14 @@
       <c r="E43">
         <v>32</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F43">
+        <f t="shared" si="1"/>
+        <v>2.6457513110645907</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>210</v>
       </c>
       <c r="B44">
@@ -11151,10 +11342,14 @@
       <c r="E44">
         <v>29</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F44">
+        <f t="shared" si="1"/>
+        <v>5.2915026221291814</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>215</v>
       </c>
       <c r="B45">
@@ -11170,10 +11365,14 @@
       <c r="E45">
         <v>29</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F45">
+        <f t="shared" si="1"/>
+        <v>3.5118845842842519</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>220</v>
       </c>
       <c r="B46">
@@ -11189,10 +11388,14 @@
       <c r="E46">
         <v>24</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F46">
+        <f t="shared" si="1"/>
+        <v>1.5275252316519465</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>225</v>
       </c>
       <c r="B47">
@@ -11208,10 +11411,14 @@
       <c r="E47">
         <v>35</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F47">
+        <f t="shared" si="1"/>
+        <v>4.1633319989322564</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>230</v>
       </c>
       <c r="B48">
@@ -11227,10 +11434,14 @@
       <c r="E48">
         <v>37</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F48">
+        <f t="shared" si="1"/>
+        <v>2.5166114784235831</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>235</v>
       </c>
       <c r="B49">
@@ -11246,10 +11457,14 @@
       <c r="E49">
         <v>46</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F49">
+        <f t="shared" si="1"/>
+        <v>3.5118845842842461</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>240</v>
       </c>
       <c r="B50">
@@ -11265,10 +11480,14 @@
       <c r="E50">
         <v>64</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F50">
+        <f t="shared" si="1"/>
+        <v>8.5049005481153639</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>245</v>
       </c>
       <c r="B51">
@@ -11284,10 +11503,14 @@
       <c r="E51">
         <v>62</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F51">
+        <f t="shared" si="1"/>
+        <v>4.5092497528228943</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>250</v>
       </c>
       <c r="B52">
@@ -11303,10 +11526,14 @@
       <c r="E52">
         <v>59</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F52">
+        <f t="shared" si="1"/>
+        <v>4.1633319989322661</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>255</v>
       </c>
       <c r="B53">
@@ -11322,10 +11549,14 @@
       <c r="E53">
         <v>73</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F53">
+        <f t="shared" si="1"/>
+        <v>3.6055512754639891</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>260</v>
       </c>
       <c r="B54">
@@ -11341,10 +11572,14 @@
       <c r="E54">
         <v>58</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F54">
+        <f t="shared" si="1"/>
+        <v>5.0332229568471671</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>265</v>
       </c>
       <c r="B55">
@@ -11360,10 +11595,14 @@
       <c r="E55">
         <v>43</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F55">
+        <f t="shared" si="1"/>
+        <v>5.8594652770823155</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>270</v>
       </c>
       <c r="B56">
@@ -11379,10 +11618,14 @@
       <c r="E56">
         <v>38</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F56">
+        <f t="shared" si="1"/>
+        <v>5.2915026221291814</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>275</v>
       </c>
       <c r="B57">
@@ -11398,10 +11641,14 @@
       <c r="E57">
         <v>36</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F57">
+        <f t="shared" si="1"/>
+        <v>4.358898943540674</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>280</v>
       </c>
       <c r="B58">
@@ -11417,10 +11664,14 @@
       <c r="E58">
         <v>40</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F58">
+        <f t="shared" si="1"/>
+        <v>1.5275252316519465</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>285</v>
       </c>
       <c r="B59">
@@ -11436,10 +11687,14 @@
       <c r="E59">
         <v>45</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F59">
+        <f t="shared" si="1"/>
+        <v>3.0550504633038935</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>290</v>
       </c>
       <c r="B60">
@@ -11455,10 +11710,14 @@
       <c r="E60">
         <v>63</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F60">
+        <f t="shared" si="1"/>
+        <v>7.5055534994651145</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>295</v>
       </c>
       <c r="B61">
@@ -11474,10 +11733,14 @@
       <c r="E61">
         <v>65</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F61">
+        <f t="shared" si="1"/>
+        <v>7.6376261582597333</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="B62">
@@ -11493,10 +11756,14 @@
       <c r="E62">
         <v>68</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F62">
+        <f t="shared" si="1"/>
+        <v>7.5055534994651349</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>305</v>
       </c>
       <c r="B63">
@@ -11512,10 +11779,14 @@
       <c r="E63">
         <v>82</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F63">
+        <f t="shared" si="1"/>
+        <v>9.6090235369330497</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>310</v>
       </c>
       <c r="B64">
@@ -11531,10 +11802,14 @@
       <c r="E64">
         <v>97</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F64">
+        <f t="shared" si="1"/>
+        <v>8.1445278152470788</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>315</v>
       </c>
       <c r="B65">
@@ -11550,10 +11825,14 @@
       <c r="E65">
         <v>77</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F65">
+        <f t="shared" si="1"/>
+        <v>6.429100507328636</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>320</v>
       </c>
       <c r="B66">
@@ -11569,14 +11848,18 @@
       <c r="E66">
         <v>77</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F66">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>325</v>
       </c>
       <c r="B67">
-        <f t="shared" ref="B67:B130" si="2">ROUND(AVERAGE(C67:E67),2)</f>
+        <f t="shared" ref="B67:B130" si="3">ROUND(AVERAGE(C67:E67),2)</f>
         <v>71</v>
       </c>
       <c r="C67">
@@ -11588,14 +11871,18 @@
       <c r="E67">
         <v>77</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F67">
+        <f t="shared" ref="F67:F130" si="4">_xlfn.STDEV.S(C67:E67)</f>
+        <v>5.5677643628300215</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68">
-        <f t="shared" ref="A68:A131" si="3">A67+5</f>
+        <f t="shared" ref="A68:A131" si="5">A67+5</f>
         <v>330</v>
       </c>
       <c r="B68">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>62.33</v>
       </c>
       <c r="C68">
@@ -11607,14 +11894,18 @@
       <c r="E68">
         <v>65</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F68">
+        <f t="shared" si="4"/>
+        <v>10.263202878893754</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69">
+        <f t="shared" si="5"/>
+        <v>335</v>
+      </c>
+      <c r="B69">
         <f t="shared" si="3"/>
-        <v>335</v>
-      </c>
-      <c r="B69">
-        <f t="shared" si="2"/>
         <v>52.33</v>
       </c>
       <c r="C69">
@@ -11626,14 +11917,18 @@
       <c r="E69">
         <v>49</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F69">
+        <f t="shared" si="4"/>
+        <v>10.408329997330648</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70">
+        <f t="shared" si="5"/>
+        <v>340</v>
+      </c>
+      <c r="B70">
         <f t="shared" si="3"/>
-        <v>340</v>
-      </c>
-      <c r="B70">
-        <f t="shared" si="2"/>
         <v>50.33</v>
       </c>
       <c r="C70">
@@ -11645,14 +11940,18 @@
       <c r="E70">
         <v>52</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F70">
+        <f t="shared" si="4"/>
+        <v>3.7859388972001828</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71">
+        <f t="shared" si="5"/>
+        <v>345</v>
+      </c>
+      <c r="B71">
         <f t="shared" si="3"/>
-        <v>345</v>
-      </c>
-      <c r="B71">
-        <f t="shared" si="2"/>
         <v>55</v>
       </c>
       <c r="C71">
@@ -11664,14 +11963,18 @@
       <c r="E71">
         <v>51</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F71">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72">
+        <f t="shared" si="5"/>
+        <v>350</v>
+      </c>
+      <c r="B72">
         <f t="shared" si="3"/>
-        <v>350</v>
-      </c>
-      <c r="B72">
-        <f t="shared" si="2"/>
         <v>63</v>
       </c>
       <c r="C72">
@@ -11683,14 +11986,18 @@
       <c r="E72">
         <v>62</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F72">
+        <f t="shared" si="4"/>
+        <v>2.6457513110645907</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73">
+        <f t="shared" si="5"/>
+        <v>355</v>
+      </c>
+      <c r="B73">
         <f t="shared" si="3"/>
-        <v>355</v>
-      </c>
-      <c r="B73">
-        <f t="shared" si="2"/>
         <v>82.33</v>
       </c>
       <c r="C73">
@@ -11702,14 +12009,18 @@
       <c r="E73">
         <v>83</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F73">
+        <f t="shared" si="4"/>
+        <v>7.0237691685684931</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74">
+        <f t="shared" si="5"/>
+        <v>360</v>
+      </c>
+      <c r="B74">
         <f t="shared" si="3"/>
-        <v>360</v>
-      </c>
-      <c r="B74">
-        <f t="shared" si="2"/>
         <v>93.33</v>
       </c>
       <c r="C74">
@@ -11721,14 +12032,18 @@
       <c r="E74">
         <v>93</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F74">
+        <f t="shared" si="4"/>
+        <v>1.5275252316519468</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75">
+        <f t="shared" si="5"/>
+        <v>365</v>
+      </c>
+      <c r="B75">
         <f t="shared" si="3"/>
-        <v>365</v>
-      </c>
-      <c r="B75">
-        <f t="shared" si="2"/>
         <v>105.67</v>
       </c>
       <c r="C75">
@@ -11740,14 +12055,18 @@
       <c r="E75">
         <v>104</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F75">
+        <f t="shared" si="4"/>
+        <v>3.7859388972001824</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76">
+        <f t="shared" si="5"/>
+        <v>370</v>
+      </c>
+      <c r="B76">
         <f t="shared" si="3"/>
-        <v>370</v>
-      </c>
-      <c r="B76">
-        <f t="shared" si="2"/>
         <v>113</v>
       </c>
       <c r="C76">
@@ -11759,14 +12078,18 @@
       <c r="E76">
         <v>102</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F76">
+        <f t="shared" si="4"/>
+        <v>9.6436507609929549</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77">
+        <f t="shared" si="5"/>
+        <v>375</v>
+      </c>
+      <c r="B77">
         <f t="shared" si="3"/>
-        <v>375</v>
-      </c>
-      <c r="B77">
-        <f t="shared" si="2"/>
         <v>105.33</v>
       </c>
       <c r="C77">
@@ -11778,14 +12101,18 @@
       <c r="E77">
         <v>104</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F77">
+        <f t="shared" si="4"/>
+        <v>6.110100926607787</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78">
+        <f t="shared" si="5"/>
+        <v>380</v>
+      </c>
+      <c r="B78">
         <f t="shared" si="3"/>
-        <v>380</v>
-      </c>
-      <c r="B78">
-        <f t="shared" si="2"/>
         <v>84.67</v>
       </c>
       <c r="C78">
@@ -11797,14 +12124,18 @@
       <c r="E78">
         <v>89</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F78">
+        <f t="shared" si="4"/>
+        <v>4.5092497528228943</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79">
+        <f t="shared" si="5"/>
+        <v>385</v>
+      </c>
+      <c r="B79">
         <f t="shared" si="3"/>
-        <v>385</v>
-      </c>
-      <c r="B79">
-        <f t="shared" si="2"/>
         <v>67.67</v>
       </c>
       <c r="C79">
@@ -11816,14 +12147,18 @@
       <c r="E79">
         <v>71</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F79">
+        <f t="shared" si="4"/>
+        <v>3.5118845842842461</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80">
+        <f t="shared" si="5"/>
+        <v>390</v>
+      </c>
+      <c r="B80">
         <f t="shared" si="3"/>
-        <v>390</v>
-      </c>
-      <c r="B80">
-        <f t="shared" si="2"/>
         <v>59.33</v>
       </c>
       <c r="C80">
@@ -11835,14 +12170,18 @@
       <c r="E80">
         <v>53</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F80">
+        <f t="shared" si="4"/>
+        <v>6.0277137733417083</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81">
+        <f t="shared" si="5"/>
+        <v>395</v>
+      </c>
+      <c r="B81">
         <f t="shared" si="3"/>
-        <v>395</v>
-      </c>
-      <c r="B81">
-        <f t="shared" si="2"/>
         <v>57</v>
       </c>
       <c r="C81">
@@ -11854,14 +12193,18 @@
       <c r="E81">
         <v>60</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F81">
+        <f t="shared" si="4"/>
+        <v>2.6457513110645907</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82">
+        <f t="shared" si="5"/>
+        <v>400</v>
+      </c>
+      <c r="B82">
         <f t="shared" si="3"/>
-        <v>400</v>
-      </c>
-      <c r="B82">
-        <f t="shared" si="2"/>
         <v>51</v>
       </c>
       <c r="C82">
@@ -11873,14 +12216,18 @@
       <c r="E82">
         <v>60</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F82">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83">
+        <f t="shared" si="5"/>
+        <v>405</v>
+      </c>
+      <c r="B83">
         <f t="shared" si="3"/>
-        <v>405</v>
-      </c>
-      <c r="B83">
-        <f t="shared" si="2"/>
         <v>58.67</v>
       </c>
       <c r="C83">
@@ -11892,14 +12239,18 @@
       <c r="E83">
         <v>52</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F83">
+        <f t="shared" si="4"/>
+        <v>7.0237691685684931</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84">
+        <f t="shared" si="5"/>
+        <v>410</v>
+      </c>
+      <c r="B84">
         <f t="shared" si="3"/>
-        <v>410</v>
-      </c>
-      <c r="B84">
-        <f t="shared" si="2"/>
         <v>78</v>
       </c>
       <c r="C84">
@@ -11911,14 +12262,18 @@
       <c r="E84">
         <v>77</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F84">
+        <f t="shared" si="4"/>
+        <v>4.5825756949558398</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85">
+        <f t="shared" si="5"/>
+        <v>415</v>
+      </c>
+      <c r="B85">
         <f t="shared" si="3"/>
-        <v>415</v>
-      </c>
-      <c r="B85">
-        <f t="shared" si="2"/>
         <v>89.67</v>
       </c>
       <c r="C85">
@@ -11930,14 +12285,18 @@
       <c r="E85">
         <v>92</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F85">
+        <f t="shared" si="4"/>
+        <v>7.7674534651540297</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86">
+        <f t="shared" si="5"/>
+        <v>420</v>
+      </c>
+      <c r="B86">
         <f t="shared" si="3"/>
-        <v>420</v>
-      </c>
-      <c r="B86">
-        <f t="shared" si="2"/>
         <v>101</v>
       </c>
       <c r="C86">
@@ -11949,14 +12308,18 @@
       <c r="E86">
         <v>106</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F86">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87">
+        <f t="shared" si="5"/>
+        <v>425</v>
+      </c>
+      <c r="B87">
         <f t="shared" si="3"/>
-        <v>425</v>
-      </c>
-      <c r="B87">
-        <f t="shared" si="2"/>
         <v>110.67</v>
       </c>
       <c r="C87">
@@ -11968,14 +12331,18 @@
       <c r="E87">
         <v>115</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F87">
+        <f t="shared" si="4"/>
+        <v>4.0414518843273806</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88">
+        <f t="shared" si="5"/>
+        <v>430</v>
+      </c>
+      <c r="B88">
         <f t="shared" si="3"/>
-        <v>430</v>
-      </c>
-      <c r="B88">
-        <f t="shared" si="2"/>
         <v>108</v>
       </c>
       <c r="C88">
@@ -11987,14 +12354,18 @@
       <c r="E88">
         <v>104</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F88">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89">
+        <f t="shared" si="5"/>
+        <v>435</v>
+      </c>
+      <c r="B89">
         <f t="shared" si="3"/>
-        <v>435</v>
-      </c>
-      <c r="B89">
-        <f t="shared" si="2"/>
         <v>110</v>
       </c>
       <c r="C89">
@@ -12006,14 +12377,18 @@
       <c r="E89">
         <v>112</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F89">
+        <f t="shared" si="4"/>
+        <v>6.2449979983983983</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90">
+        <f t="shared" si="5"/>
+        <v>440</v>
+      </c>
+      <c r="B90">
         <f t="shared" si="3"/>
-        <v>440</v>
-      </c>
-      <c r="B90">
-        <f t="shared" si="2"/>
         <v>91.67</v>
       </c>
       <c r="C90">
@@ -12025,14 +12400,18 @@
       <c r="E90">
         <v>87</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F90">
+        <f t="shared" si="4"/>
+        <v>8.9628864398325021</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91">
+        <f t="shared" si="5"/>
+        <v>445</v>
+      </c>
+      <c r="B91">
         <f t="shared" si="3"/>
-        <v>445</v>
-      </c>
-      <c r="B91">
-        <f t="shared" si="2"/>
         <v>74.67</v>
       </c>
       <c r="C91">
@@ -12044,14 +12423,18 @@
       <c r="E91">
         <v>71</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F91">
+        <f t="shared" si="4"/>
+        <v>3.214550253664318</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92">
+        <f t="shared" si="5"/>
+        <v>450</v>
+      </c>
+      <c r="B92">
         <f t="shared" si="3"/>
-        <v>450</v>
-      </c>
-      <c r="B92">
-        <f t="shared" si="2"/>
         <v>61.67</v>
       </c>
       <c r="C92">
@@ -12063,14 +12446,18 @@
       <c r="E92">
         <v>62</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F92">
+        <f t="shared" si="4"/>
+        <v>4.5092497528228943</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93">
+        <f t="shared" si="5"/>
+        <v>455</v>
+      </c>
+      <c r="B93">
         <f t="shared" si="3"/>
-        <v>455</v>
-      </c>
-      <c r="B93">
-        <f t="shared" si="2"/>
         <v>44</v>
       </c>
       <c r="C93">
@@ -12082,14 +12469,18 @@
       <c r="E93">
         <v>41</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F93">
+        <f t="shared" si="4"/>
+        <v>4.358898943540674</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94">
+        <f t="shared" si="5"/>
+        <v>460</v>
+      </c>
+      <c r="B94">
         <f t="shared" si="3"/>
-        <v>460</v>
-      </c>
-      <c r="B94">
-        <f t="shared" si="2"/>
         <v>52</v>
       </c>
       <c r="C94">
@@ -12101,14 +12492,18 @@
       <c r="E94">
         <v>55</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F94">
+        <f t="shared" si="4"/>
+        <v>4.358898943540674</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95">
+        <f t="shared" si="5"/>
+        <v>465</v>
+      </c>
+      <c r="B95">
         <f t="shared" si="3"/>
-        <v>465</v>
-      </c>
-      <c r="B95">
-        <f t="shared" si="2"/>
         <v>54.67</v>
       </c>
       <c r="C95">
@@ -12120,14 +12515,18 @@
       <c r="E95">
         <v>53</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F95">
+        <f t="shared" si="4"/>
+        <v>1.5275252316519465</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96">
+        <f t="shared" si="5"/>
+        <v>470</v>
+      </c>
+      <c r="B96">
         <f t="shared" si="3"/>
-        <v>470</v>
-      </c>
-      <c r="B96">
-        <f t="shared" si="2"/>
         <v>84.33</v>
       </c>
       <c r="C96">
@@ -12139,14 +12538,18 @@
       <c r="E96">
         <v>93</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F96">
+        <f t="shared" si="4"/>
+        <v>7.5718777944003648</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97">
+        <f t="shared" si="5"/>
+        <v>475</v>
+      </c>
+      <c r="B97">
         <f t="shared" si="3"/>
-        <v>475</v>
-      </c>
-      <c r="B97">
-        <f t="shared" si="2"/>
         <v>96.33</v>
       </c>
       <c r="C97">
@@ -12158,14 +12561,18 @@
       <c r="E97">
         <v>96</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F97">
+        <f t="shared" si="4"/>
+        <v>3.5118845842842461</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98">
+        <f t="shared" si="5"/>
+        <v>480</v>
+      </c>
+      <c r="B98">
         <f t="shared" si="3"/>
-        <v>480</v>
-      </c>
-      <c r="B98">
-        <f t="shared" si="2"/>
         <v>94.33</v>
       </c>
       <c r="C98">
@@ -12177,14 +12584,18 @@
       <c r="E98">
         <v>97</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F98">
+        <f t="shared" si="4"/>
+        <v>5.5075705472861021</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99">
+        <f t="shared" si="5"/>
+        <v>485</v>
+      </c>
+      <c r="B99">
         <f t="shared" si="3"/>
-        <v>485</v>
-      </c>
-      <c r="B99">
-        <f t="shared" si="2"/>
         <v>98.33</v>
       </c>
       <c r="C99">
@@ -12196,14 +12607,18 @@
       <c r="E99">
         <v>92</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F99">
+        <f t="shared" si="4"/>
+        <v>6.5064070986477116</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100">
+        <f t="shared" si="5"/>
+        <v>490</v>
+      </c>
+      <c r="B100">
         <f t="shared" si="3"/>
-        <v>490</v>
-      </c>
-      <c r="B100">
-        <f t="shared" si="2"/>
         <v>89.33</v>
       </c>
       <c r="C100">
@@ -12215,14 +12630,18 @@
       <c r="E100">
         <v>87</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F100">
+        <f t="shared" si="4"/>
+        <v>6.8068592855540455</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101">
+        <f t="shared" si="5"/>
+        <v>495</v>
+      </c>
+      <c r="B101">
         <f t="shared" si="3"/>
-        <v>495</v>
-      </c>
-      <c r="B101">
-        <f t="shared" si="2"/>
         <v>81.33</v>
       </c>
       <c r="C101">
@@ -12234,14 +12653,18 @@
       <c r="E101">
         <v>74</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F101">
+        <f t="shared" si="4"/>
+        <v>6.429100507328636</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102">
+        <f t="shared" si="5"/>
+        <v>500</v>
+      </c>
+      <c r="B102">
         <f t="shared" si="3"/>
-        <v>500</v>
-      </c>
-      <c r="B102">
-        <f t="shared" si="2"/>
         <v>67.33</v>
       </c>
       <c r="C102">
@@ -12253,14 +12676,18 @@
       <c r="E102">
         <v>80</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F102">
+        <f t="shared" si="4"/>
+        <v>11.150485789118473</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103">
+        <f t="shared" si="5"/>
+        <v>505</v>
+      </c>
+      <c r="B103">
         <f t="shared" si="3"/>
-        <v>505</v>
-      </c>
-      <c r="B103">
-        <f t="shared" si="2"/>
         <v>46</v>
       </c>
       <c r="C103">
@@ -12272,14 +12699,18 @@
       <c r="E103">
         <v>51</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F103">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104">
+        <f t="shared" si="5"/>
+        <v>510</v>
+      </c>
+      <c r="B104">
         <f t="shared" si="3"/>
-        <v>510</v>
-      </c>
-      <c r="B104">
-        <f t="shared" si="2"/>
         <v>48.67</v>
       </c>
       <c r="C104">
@@ -12291,14 +12722,18 @@
       <c r="E104">
         <v>51</v>
       </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F104">
+        <f t="shared" si="4"/>
+        <v>2.5166114784235831</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105">
+        <f t="shared" si="5"/>
+        <v>515</v>
+      </c>
+      <c r="B105">
         <f t="shared" si="3"/>
-        <v>515</v>
-      </c>
-      <c r="B105">
-        <f t="shared" si="2"/>
         <v>45</v>
       </c>
       <c r="C105">
@@ -12310,14 +12745,18 @@
       <c r="E105">
         <v>43</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F105">
+        <f t="shared" si="4"/>
+        <v>4.358898943540674</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106">
+        <f t="shared" si="5"/>
+        <v>520</v>
+      </c>
+      <c r="B106">
         <f t="shared" si="3"/>
-        <v>520</v>
-      </c>
-      <c r="B106">
-        <f t="shared" si="2"/>
         <v>49.67</v>
       </c>
       <c r="C106">
@@ -12329,14 +12768,18 @@
       <c r="E106">
         <v>50</v>
       </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F106">
+        <f t="shared" si="4"/>
+        <v>0.57735026918962584</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107">
+        <f t="shared" si="5"/>
+        <v>525</v>
+      </c>
+      <c r="B107">
         <f t="shared" si="3"/>
-        <v>525</v>
-      </c>
-      <c r="B107">
-        <f t="shared" si="2"/>
         <v>48.67</v>
       </c>
       <c r="C107">
@@ -12348,14 +12791,18 @@
       <c r="E107">
         <v>49</v>
       </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F107">
+        <f t="shared" si="4"/>
+        <v>3.5118845842842465</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108">
+        <f t="shared" si="5"/>
+        <v>530</v>
+      </c>
+      <c r="B108">
         <f t="shared" si="3"/>
-        <v>530</v>
-      </c>
-      <c r="B108">
-        <f t="shared" si="2"/>
         <v>54.33</v>
       </c>
       <c r="C108">
@@ -12367,14 +12814,18 @@
       <c r="E108">
         <v>56</v>
       </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F108">
+        <f t="shared" si="4"/>
+        <v>6.6583281184793934</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109">
+        <f t="shared" si="5"/>
+        <v>535</v>
+      </c>
+      <c r="B109">
         <f t="shared" si="3"/>
-        <v>535</v>
-      </c>
-      <c r="B109">
-        <f t="shared" si="2"/>
         <v>69.33</v>
       </c>
       <c r="C109">
@@ -12386,14 +12837,18 @@
       <c r="E109">
         <v>68</v>
       </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F109">
+        <f t="shared" si="4"/>
+        <v>3.214550253664318</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110">
+        <f t="shared" si="5"/>
+        <v>540</v>
+      </c>
+      <c r="B110">
         <f t="shared" si="3"/>
-        <v>540</v>
-      </c>
-      <c r="B110">
-        <f t="shared" si="2"/>
         <v>71.33</v>
       </c>
       <c r="C110">
@@ -12405,14 +12860,18 @@
       <c r="E110">
         <v>72</v>
       </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F110">
+        <f t="shared" si="4"/>
+        <v>2.0816659994661326</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111">
+        <f t="shared" si="5"/>
+        <v>545</v>
+      </c>
+      <c r="B111">
         <f t="shared" si="3"/>
-        <v>545</v>
-      </c>
-      <c r="B111">
-        <f t="shared" si="2"/>
         <v>76</v>
       </c>
       <c r="C111">
@@ -12424,14 +12883,18 @@
       <c r="E111">
         <v>81</v>
       </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F111">
+        <f t="shared" si="4"/>
+        <v>5.5677643628300215</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112">
+        <f t="shared" si="5"/>
+        <v>550</v>
+      </c>
+      <c r="B112">
         <f t="shared" si="3"/>
-        <v>550</v>
-      </c>
-      <c r="B112">
-        <f t="shared" si="2"/>
         <v>80.33</v>
       </c>
       <c r="C112">
@@ -12443,14 +12906,18 @@
       <c r="E112">
         <v>78</v>
       </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F112">
+        <f t="shared" si="4"/>
+        <v>2.0816659994661331</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113">
+        <f t="shared" si="5"/>
+        <v>555</v>
+      </c>
+      <c r="B113">
         <f t="shared" si="3"/>
-        <v>555</v>
-      </c>
-      <c r="B113">
-        <f t="shared" si="2"/>
         <v>82.33</v>
       </c>
       <c r="C113">
@@ -12462,14 +12929,18 @@
       <c r="E113">
         <v>96</v>
       </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F113">
+        <f t="shared" si="4"/>
+        <v>12.662279942148411</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114">
+        <f t="shared" si="5"/>
+        <v>560</v>
+      </c>
+      <c r="B114">
         <f t="shared" si="3"/>
-        <v>560</v>
-      </c>
-      <c r="B114">
-        <f t="shared" si="2"/>
         <v>72.67</v>
       </c>
       <c r="C114">
@@ -12481,14 +12952,18 @@
       <c r="E114">
         <v>69</v>
       </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F114">
+        <f t="shared" si="4"/>
+        <v>5.5075705472861021</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115">
+        <f t="shared" si="5"/>
+        <v>565</v>
+      </c>
+      <c r="B115">
         <f t="shared" si="3"/>
-        <v>565</v>
-      </c>
-      <c r="B115">
-        <f t="shared" si="2"/>
         <v>54</v>
       </c>
       <c r="C115">
@@ -12500,14 +12975,18 @@
       <c r="E115">
         <v>58</v>
       </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F115">
+        <f t="shared" si="4"/>
+        <v>3.6055512754639891</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116">
+        <f t="shared" si="5"/>
+        <v>570</v>
+      </c>
+      <c r="B116">
         <f t="shared" si="3"/>
-        <v>570</v>
-      </c>
-      <c r="B116">
-        <f t="shared" si="2"/>
         <v>44.67</v>
       </c>
       <c r="C116">
@@ -12519,14 +12998,18 @@
       <c r="E116">
         <v>39</v>
       </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F116">
+        <f t="shared" si="4"/>
+        <v>5.1316014394468841</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117">
+        <f t="shared" si="5"/>
+        <v>575</v>
+      </c>
+      <c r="B117">
         <f t="shared" si="3"/>
-        <v>575</v>
-      </c>
-      <c r="B117">
-        <f t="shared" si="2"/>
         <v>39.33</v>
       </c>
       <c r="C117">
@@ -12538,14 +13021,18 @@
       <c r="E117">
         <v>33</v>
       </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F117">
+        <f t="shared" si="4"/>
+        <v>6.0277137733417208</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118">
+        <f t="shared" si="5"/>
+        <v>580</v>
+      </c>
+      <c r="B118">
         <f t="shared" si="3"/>
-        <v>580</v>
-      </c>
-      <c r="B118">
-        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="C118">
@@ -12557,14 +13044,18 @@
       <c r="E118">
         <v>38</v>
       </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F118">
+        <f t="shared" si="4"/>
+        <v>4.358898943540674</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119">
+        <f t="shared" si="5"/>
+        <v>585</v>
+      </c>
+      <c r="B119">
         <f t="shared" si="3"/>
-        <v>585</v>
-      </c>
-      <c r="B119">
-        <f t="shared" si="2"/>
         <v>51.33</v>
       </c>
       <c r="C119">
@@ -12576,14 +13067,18 @@
       <c r="E119">
         <v>60</v>
       </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F119">
+        <f t="shared" si="4"/>
+        <v>9.0184995056457975</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120">
+        <f t="shared" si="5"/>
+        <v>590</v>
+      </c>
+      <c r="B120">
         <f t="shared" si="3"/>
-        <v>590</v>
-      </c>
-      <c r="B120">
-        <f t="shared" si="2"/>
         <v>52.33</v>
       </c>
       <c r="C120">
@@ -12595,14 +13090,18 @@
       <c r="E120">
         <v>61</v>
       </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F120">
+        <f t="shared" si="4"/>
+        <v>8.0829037686547416</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121">
+        <f t="shared" si="5"/>
+        <v>595</v>
+      </c>
+      <c r="B121">
         <f t="shared" si="3"/>
-        <v>595</v>
-      </c>
-      <c r="B121">
-        <f t="shared" si="2"/>
         <v>63</v>
       </c>
       <c r="C121">
@@ -12614,14 +13113,18 @@
       <c r="E121">
         <v>66</v>
       </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F121">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122">
+        <f t="shared" si="5"/>
+        <v>600</v>
+      </c>
+      <c r="B122">
         <f t="shared" si="3"/>
-        <v>600</v>
-      </c>
-      <c r="B122">
-        <f t="shared" si="2"/>
         <v>56.33</v>
       </c>
       <c r="C122">
@@ -12633,14 +13136,18 @@
       <c r="E122">
         <v>54</v>
       </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F122">
+        <f t="shared" si="4"/>
+        <v>2.5166114784235831</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123">
+        <f t="shared" si="5"/>
+        <v>605</v>
+      </c>
+      <c r="B123">
         <f t="shared" si="3"/>
-        <v>605</v>
-      </c>
-      <c r="B123">
-        <f t="shared" si="2"/>
         <v>53.67</v>
       </c>
       <c r="C123">
@@ -12652,14 +13159,18 @@
       <c r="E123">
         <v>51</v>
       </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F123">
+        <f t="shared" si="4"/>
+        <v>3.0550504633038931</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124">
+        <f t="shared" si="5"/>
+        <v>610</v>
+      </c>
+      <c r="B124">
         <f t="shared" si="3"/>
-        <v>610</v>
-      </c>
-      <c r="B124">
-        <f t="shared" si="2"/>
         <v>48.33</v>
       </c>
       <c r="C124">
@@ -12671,14 +13182,18 @@
       <c r="E124">
         <v>48</v>
       </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F124">
+        <f t="shared" si="4"/>
+        <v>1.5275252316519465</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125">
+        <f t="shared" si="5"/>
+        <v>615</v>
+      </c>
+      <c r="B125">
         <f t="shared" si="3"/>
-        <v>615</v>
-      </c>
-      <c r="B125">
-        <f t="shared" si="2"/>
         <v>42</v>
       </c>
       <c r="C125">
@@ -12690,14 +13205,18 @@
       <c r="E125">
         <v>42</v>
       </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F125">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126">
+        <f t="shared" si="5"/>
+        <v>620</v>
+      </c>
+      <c r="B126">
         <f t="shared" si="3"/>
-        <v>620</v>
-      </c>
-      <c r="B126">
-        <f t="shared" si="2"/>
         <v>35</v>
       </c>
       <c r="C126">
@@ -12709,14 +13228,18 @@
       <c r="E126">
         <v>36</v>
       </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F126">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127">
+        <f t="shared" si="5"/>
+        <v>625</v>
+      </c>
+      <c r="B127">
         <f t="shared" si="3"/>
-        <v>625</v>
-      </c>
-      <c r="B127">
-        <f t="shared" si="2"/>
         <v>37</v>
       </c>
       <c r="C127">
@@ -12728,14 +13251,18 @@
       <c r="E127">
         <v>31</v>
       </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F127">
+        <f t="shared" si="4"/>
+        <v>5.2915026221291814</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128">
+        <f t="shared" si="5"/>
+        <v>630</v>
+      </c>
+      <c r="B128">
         <f t="shared" si="3"/>
-        <v>630</v>
-      </c>
-      <c r="B128">
-        <f t="shared" si="2"/>
         <v>30.67</v>
       </c>
       <c r="C128">
@@ -12747,14 +13274,18 @@
       <c r="E128">
         <v>36</v>
       </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F128">
+        <f t="shared" si="4"/>
+        <v>4.7258156262526008</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129">
+        <f t="shared" si="5"/>
+        <v>635</v>
+      </c>
+      <c r="B129">
         <f t="shared" si="3"/>
-        <v>635</v>
-      </c>
-      <c r="B129">
-        <f t="shared" si="2"/>
         <v>34.33</v>
       </c>
       <c r="C129">
@@ -12766,14 +13297,18 @@
       <c r="E129">
         <v>32</v>
       </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F129">
+        <f t="shared" si="4"/>
+        <v>2.5166114784235831</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130">
+        <f t="shared" si="5"/>
+        <v>640</v>
+      </c>
+      <c r="B130">
         <f t="shared" si="3"/>
-        <v>640</v>
-      </c>
-      <c r="B130">
-        <f t="shared" si="2"/>
         <v>39.33</v>
       </c>
       <c r="C130">
@@ -12785,14 +13320,18 @@
       <c r="E130">
         <v>41</v>
       </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F130">
+        <f t="shared" si="4"/>
+        <v>1.5275252316519465</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>645</v>
       </c>
       <c r="B131">
-        <f t="shared" ref="B131:B193" si="4">ROUND(AVERAGE(C131:E131),2)</f>
+        <f t="shared" ref="B131:B174" si="6">ROUND(AVERAGE(C131:E131),2)</f>
         <v>37.33</v>
       </c>
       <c r="C131">
@@ -12804,14 +13343,18 @@
       <c r="E131">
         <v>39</v>
       </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F131">
+        <f t="shared" ref="F131:F174" si="7">_xlfn.STDEV.S(C131:E131)</f>
+        <v>1.5275252316519465</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132">
-        <f t="shared" ref="A132:A193" si="5">A131+5</f>
+        <f t="shared" ref="A132:A174" si="8">A131+5</f>
         <v>650</v>
       </c>
       <c r="B132">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>39.33</v>
       </c>
       <c r="C132">
@@ -12823,14 +13366,18 @@
       <c r="E132">
         <v>43</v>
       </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F132">
+        <f t="shared" si="7"/>
+        <v>3.5118845842842461</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>655</v>
       </c>
       <c r="B133">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>41</v>
       </c>
       <c r="C133">
@@ -12842,14 +13389,18 @@
       <c r="E133">
         <v>46</v>
       </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F133">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>660</v>
       </c>
       <c r="B134">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>39.67</v>
       </c>
       <c r="C134">
@@ -12861,14 +13412,18 @@
       <c r="E134">
         <v>40</v>
       </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F134">
+        <f t="shared" si="7"/>
+        <v>1.5275252316519465</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>665</v>
       </c>
       <c r="B135">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>34.67</v>
       </c>
       <c r="C135">
@@ -12880,14 +13435,18 @@
       <c r="E135">
         <v>39</v>
       </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F135">
+        <f t="shared" si="7"/>
+        <v>4.0414518843273806</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>670</v>
       </c>
       <c r="B136">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>31</v>
       </c>
       <c r="C136">
@@ -12899,14 +13458,18 @@
       <c r="E136">
         <v>31</v>
       </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F136">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>675</v>
       </c>
       <c r="B137">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>29.33</v>
       </c>
       <c r="C137">
@@ -12918,14 +13481,18 @@
       <c r="E137">
         <v>32</v>
       </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F137">
+        <f t="shared" si="7"/>
+        <v>4.6188021535169979</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>680</v>
       </c>
       <c r="B138">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>32.33</v>
       </c>
       <c r="C138">
@@ -12937,14 +13504,18 @@
       <c r="E138">
         <v>31</v>
       </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F138">
+        <f t="shared" si="7"/>
+        <v>4.1633319989322564</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>685</v>
       </c>
       <c r="B139">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>28</v>
       </c>
       <c r="C139">
@@ -12956,14 +13527,18 @@
       <c r="E139">
         <v>30</v>
       </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F139">
+        <f t="shared" si="7"/>
+        <v>2.6457513110645907</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>690</v>
       </c>
       <c r="B140">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>28</v>
       </c>
       <c r="C140">
@@ -12975,14 +13550,18 @@
       <c r="E140">
         <v>23</v>
       </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F140">
+        <f t="shared" si="7"/>
+        <v>4.358898943540674</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>695</v>
       </c>
       <c r="B141">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>26</v>
       </c>
       <c r="C141">
@@ -12994,14 +13573,18 @@
       <c r="E141">
         <v>25</v>
       </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F141">
+        <f t="shared" si="7"/>
+        <v>2.6457513110645907</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>700</v>
       </c>
       <c r="B142">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>26.67</v>
       </c>
       <c r="C142">
@@ -13013,14 +13596,18 @@
       <c r="E142">
         <v>27</v>
       </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F142">
+        <f t="shared" si="7"/>
+        <v>0.57735026918962584</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>705</v>
       </c>
       <c r="B143">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>27</v>
       </c>
       <c r="C143">
@@ -13032,14 +13619,18 @@
       <c r="E143">
         <v>28</v>
       </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F143">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>710</v>
       </c>
       <c r="B144">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>26.33</v>
       </c>
       <c r="C144">
@@ -13051,14 +13642,18 @@
       <c r="E144">
         <v>29</v>
       </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F144">
+        <f t="shared" si="7"/>
+        <v>2.5166114784235836</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>715</v>
       </c>
       <c r="B145">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>22</v>
       </c>
       <c r="C145">
@@ -13070,14 +13665,18 @@
       <c r="E145">
         <v>21</v>
       </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F145">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>720</v>
       </c>
       <c r="B146">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>25.33</v>
       </c>
       <c r="C146">
@@ -13089,14 +13688,18 @@
       <c r="E146">
         <v>24</v>
       </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F146">
+        <f t="shared" si="7"/>
+        <v>1.5275252316519465</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>725</v>
       </c>
       <c r="B147">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>23.33</v>
       </c>
       <c r="C147">
@@ -13108,14 +13711,18 @@
       <c r="E147">
         <v>23</v>
       </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F147">
+        <f t="shared" si="7"/>
+        <v>1.5275252316519468</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>730</v>
       </c>
       <c r="B148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>26.67</v>
       </c>
       <c r="C148">
@@ -13127,14 +13734,18 @@
       <c r="E148">
         <v>24</v>
       </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F148">
+        <f t="shared" si="7"/>
+        <v>2.5166114784235836</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>735</v>
       </c>
       <c r="B149">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="C149">
@@ -13146,14 +13757,18 @@
       <c r="E149">
         <v>23</v>
       </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F149">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>740</v>
       </c>
       <c r="B150">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>21.67</v>
       </c>
       <c r="C150">
@@ -13165,14 +13780,18 @@
       <c r="E150">
         <v>21</v>
       </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F150">
+        <f t="shared" si="7"/>
+        <v>2.0816659994661331</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>745</v>
       </c>
       <c r="B151">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>18.670000000000002</v>
       </c>
       <c r="C151">
@@ -13184,14 +13803,18 @@
       <c r="E151">
         <v>19</v>
       </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F151">
+        <f t="shared" si="7"/>
+        <v>0.57735026918962584</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>750</v>
       </c>
       <c r="B152">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>21</v>
       </c>
       <c r="C152">
@@ -13203,14 +13826,18 @@
       <c r="E152">
         <v>20</v>
       </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F152">
+        <f t="shared" si="7"/>
+        <v>2.6457513110645907</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>755</v>
       </c>
       <c r="B153">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>22.67</v>
       </c>
       <c r="C153">
@@ -13222,14 +13849,18 @@
       <c r="E153">
         <v>25</v>
       </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F153">
+        <f t="shared" si="7"/>
+        <v>2.0816659994661331</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>760</v>
       </c>
       <c r="B154">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>21</v>
       </c>
       <c r="C154">
@@ -13241,14 +13872,18 @@
       <c r="E154">
         <v>21</v>
       </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F154">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>765</v>
       </c>
       <c r="B155">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="C155">
@@ -13260,14 +13895,18 @@
       <c r="E155">
         <v>21</v>
       </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F155">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>770</v>
       </c>
       <c r="B156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="C156">
@@ -13279,14 +13918,18 @@
       <c r="E156">
         <v>19</v>
       </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F156">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>775</v>
       </c>
       <c r="B157">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>12.33</v>
       </c>
       <c r="C157">
@@ -13298,14 +13941,18 @@
       <c r="E157">
         <v>13</v>
       </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F157">
+        <f t="shared" si="7"/>
+        <v>3.0550504633038948</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>780</v>
       </c>
       <c r="B158">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>18.329999999999998</v>
       </c>
       <c r="C158">
@@ -13317,14 +13964,18 @@
       <c r="E158">
         <v>20</v>
       </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F158">
+        <f t="shared" si="7"/>
+        <v>2.0816659994661331</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>785</v>
       </c>
       <c r="B159">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>14</v>
       </c>
       <c r="C159">
@@ -13336,14 +13987,18 @@
       <c r="E159">
         <v>11</v>
       </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F159">
+        <f t="shared" si="7"/>
+        <v>5.196152422706632</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>790</v>
       </c>
       <c r="B160">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>16.329999999999998</v>
       </c>
       <c r="C160">
@@ -13355,14 +14010,18 @@
       <c r="E160">
         <v>14</v>
       </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F160">
+        <f t="shared" si="7"/>
+        <v>2.0816659994661282</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>795</v>
       </c>
       <c r="B161">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>15.67</v>
       </c>
       <c r="C161">
@@ -13374,14 +14033,18 @@
       <c r="E161">
         <v>14</v>
       </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F161">
+        <f t="shared" si="7"/>
+        <v>2.0816659994661282</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>800</v>
       </c>
       <c r="B162">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>13.67</v>
       </c>
       <c r="C162">
@@ -13393,14 +14056,18 @@
       <c r="E162">
         <v>17</v>
       </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F162">
+        <f t="shared" si="7"/>
+        <v>3.0550504633038904</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>805</v>
       </c>
       <c r="B163">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>15.67</v>
       </c>
       <c r="C163">
@@ -13412,14 +14079,18 @@
       <c r="E163">
         <v>18</v>
       </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F163">
+        <f t="shared" si="7"/>
+        <v>4.0414518843273779</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>810</v>
       </c>
       <c r="B164">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>12.33</v>
       </c>
       <c r="C164">
@@ -13431,14 +14102,18 @@
       <c r="E164">
         <v>11</v>
       </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F164">
+        <f t="shared" si="7"/>
+        <v>2.3094010767585051</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>815</v>
       </c>
       <c r="B165">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="C165">
@@ -13450,14 +14125,18 @@
       <c r="E165">
         <v>14</v>
       </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F165">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>820</v>
       </c>
       <c r="B166">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="C166">
@@ -13469,14 +14148,18 @@
       <c r="E166">
         <v>12</v>
       </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F166">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>825</v>
       </c>
       <c r="B167">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="C167">
@@ -13488,14 +14171,18 @@
       <c r="E167">
         <v>13</v>
       </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F167">
+        <f t="shared" si="7"/>
+        <v>2.6457513110645907</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>830</v>
       </c>
       <c r="B168">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="C168">
@@ -13507,14 +14194,18 @@
       <c r="E168">
         <v>6</v>
       </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F168">
+        <f t="shared" si="7"/>
+        <v>4.358898943540674</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>835</v>
       </c>
       <c r="B169">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>9.33</v>
       </c>
       <c r="C169">
@@ -13526,14 +14217,18 @@
       <c r="E169">
         <v>9</v>
       </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F169">
+        <f t="shared" si="7"/>
+        <v>0.57735026918962573</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>840</v>
       </c>
       <c r="B170">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>7.33</v>
       </c>
       <c r="C170">
@@ -13545,14 +14240,18 @@
       <c r="E170">
         <v>8</v>
       </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F170">
+        <f t="shared" si="7"/>
+        <v>1.1547005383792495</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>845</v>
       </c>
       <c r="B171">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>7.33</v>
       </c>
       <c r="C171">
@@ -13564,14 +14263,18 @@
       <c r="E171">
         <v>5</v>
       </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F171">
+        <f t="shared" si="7"/>
+        <v>3.2145502536643176</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>850</v>
       </c>
       <c r="B172">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="C172">
@@ -13583,14 +14286,18 @@
       <c r="E172">
         <v>7</v>
       </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F172">
+        <f t="shared" si="7"/>
+        <v>2.6457513110645907</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>855</v>
       </c>
       <c r="B173">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>5.33</v>
       </c>
       <c r="C173">
@@ -13602,14 +14309,18 @@
       <c r="E173">
         <v>4</v>
       </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F173">
+        <f t="shared" si="7"/>
+        <v>1.5275252316519474</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>860</v>
       </c>
       <c r="B174">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="C174">
@@ -13620,6 +14331,10 @@
       </c>
       <c r="E174">
         <v>4</v>
+      </c>
+      <c r="F174">
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -13630,18 +14345,24 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B17E9AE9-9CED-4B37-AC92-28F53DCE2285}">
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:P80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
@@ -13658,17 +14379,17 @@
       <c r="E2">
         <v>9</v>
       </c>
-      <c r="G2">
-        <f>MOD(A2,50)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F2">
+        <f>_xlfn.STDEV.S(C2:E2)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>20</v>
       </c>
       <c r="B3">
-        <f t="shared" ref="B3:B66" si="0">AVERAGE(C3:E3)</f>
+        <f t="shared" ref="B3:B42" si="0">AVERAGE(C3:E3)</f>
         <v>5.333333333333333</v>
       </c>
       <c r="C3">
@@ -13680,12 +14401,12 @@
       <c r="E3">
         <v>5</v>
       </c>
-      <c r="G3">
-        <f t="shared" ref="G3:G66" si="1">MOD(A3,50)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F3">
+        <f t="shared" ref="F3:F42" si="1">_xlfn.STDEV.S(C3:E3)</f>
+        <v>2.5166114784235836</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>40</v>
       </c>
@@ -13702,12 +14423,16 @@
       <c r="E4">
         <v>6</v>
       </c>
-      <c r="G4">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <f>MAX(E2:E193)</f>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>A4+20</f>
         <v>60</v>
@@ -13725,14 +14450,14 @@
       <c r="E5">
         <v>4</v>
       </c>
-      <c r="G5">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>1.1547005383792526</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
-        <f t="shared" ref="A6:A69" si="2">A5+20</f>
+        <f t="shared" ref="A6:A42" si="2">A5+20</f>
         <v>80</v>
       </c>
       <c r="B6">
@@ -13748,12 +14473,12 @@
       <c r="E6">
         <v>3</v>
       </c>
-      <c r="G6">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="2"/>
         <v>100</v>
@@ -13771,12 +14496,12 @@
       <c r="E7">
         <v>5</v>
       </c>
-      <c r="G7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="2"/>
         <v>120</v>
@@ -13794,12 +14519,12 @@
       <c r="E8">
         <v>6</v>
       </c>
-      <c r="G8">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="2"/>
         <v>140</v>
@@ -13817,12 +14542,12 @@
       <c r="E9">
         <v>9</v>
       </c>
-      <c r="G9">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F9">
+        <f t="shared" si="1"/>
+        <v>2.0816659994661317</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="2"/>
         <v>160</v>
@@ -13840,12 +14565,12 @@
       <c r="E10">
         <v>15</v>
       </c>
-      <c r="G10">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F10">
+        <f t="shared" si="1"/>
+        <v>3.0550504633038948</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="2"/>
         <v>180</v>
@@ -13863,12 +14588,12 @@
       <c r="E11">
         <v>14</v>
       </c>
-      <c r="G11">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F11">
+        <f t="shared" si="1"/>
+        <v>3.6055512754639891</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="2"/>
         <v>200</v>
@@ -13886,12 +14611,12 @@
       <c r="E12">
         <v>12</v>
       </c>
-      <c r="G12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F12">
+        <f t="shared" si="1"/>
+        <v>2.6457513110645907</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="2"/>
         <v>220</v>
@@ -13909,12 +14634,12 @@
       <c r="E13">
         <v>18</v>
       </c>
-      <c r="G13">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F13">
+        <f t="shared" si="1"/>
+        <v>2.6457513110645907</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="2"/>
         <v>240</v>
@@ -13932,12 +14657,12 @@
       <c r="E14">
         <v>27</v>
       </c>
-      <c r="G14">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F14">
+        <f t="shared" si="1"/>
+        <v>1.5275252316519465</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15">
         <f t="shared" si="2"/>
         <v>260</v>
@@ -13955,12 +14680,12 @@
       <c r="E15">
         <v>23</v>
       </c>
-      <c r="G15">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F15">
+        <f t="shared" si="1"/>
+        <v>5.5677643628300215</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16">
         <f t="shared" si="2"/>
         <v>280</v>
@@ -13978,12 +14703,12 @@
       <c r="E16">
         <v>34</v>
       </c>
-      <c r="G16">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F16">
+        <f t="shared" si="1"/>
+        <v>3.2145502536643185</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <f t="shared" si="2"/>
         <v>300</v>
@@ -14001,12 +14726,12 @@
       <c r="E17">
         <v>45</v>
       </c>
-      <c r="G17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F17">
+        <f t="shared" si="1"/>
+        <v>4.358898943540674</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <f t="shared" si="2"/>
         <v>320</v>
@@ -14024,12 +14749,12 @@
       <c r="E18">
         <v>48</v>
       </c>
-      <c r="G18">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F18">
+        <f t="shared" si="1"/>
+        <v>1.5275252316519465</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <f t="shared" si="2"/>
         <v>340</v>
@@ -14047,12 +14772,12 @@
       <c r="E19">
         <v>48</v>
       </c>
-      <c r="G19">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F19">
+        <f t="shared" si="1"/>
+        <v>6.3508529610858835</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <f t="shared" si="2"/>
         <v>360</v>
@@ -14070,12 +14795,12 @@
       <c r="E20">
         <v>62</v>
       </c>
-      <c r="G20">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F20">
+        <f t="shared" si="1"/>
+        <v>3.6055512754639891</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <f t="shared" si="2"/>
         <v>380</v>
@@ -14093,12 +14818,12 @@
       <c r="E21">
         <v>63</v>
       </c>
-      <c r="G21">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F21">
+        <f t="shared" si="1"/>
+        <v>6.4291005073286369</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <f t="shared" si="2"/>
         <v>400</v>
@@ -14116,12 +14841,12 @@
       <c r="E22">
         <v>57</v>
       </c>
-      <c r="G22">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F22">
+        <f t="shared" si="1"/>
+        <v>2.6457513110645907</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <f t="shared" si="2"/>
         <v>420</v>
@@ -14139,12 +14864,12 @@
       <c r="E23">
         <v>55</v>
       </c>
-      <c r="G23">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F23">
+        <f t="shared" si="1"/>
+        <v>3.0550504633038931</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <f t="shared" si="2"/>
         <v>440</v>
@@ -14162,12 +14887,12 @@
       <c r="E24">
         <v>55</v>
       </c>
-      <c r="G24">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F24">
+        <f t="shared" si="1"/>
+        <v>5.196152422706632</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <f t="shared" si="2"/>
         <v>460</v>
@@ -14185,12 +14910,12 @@
       <c r="E25">
         <v>56</v>
       </c>
-      <c r="G25">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F25">
+        <f t="shared" si="1"/>
+        <v>2.5166114784235831</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <f t="shared" si="2"/>
         <v>480</v>
@@ -14208,12 +14933,12 @@
       <c r="E26">
         <v>52</v>
       </c>
-      <c r="G26">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F26">
+        <f t="shared" si="1"/>
+        <v>3.7859388972001828</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <f t="shared" si="2"/>
         <v>500</v>
@@ -14231,12 +14956,12 @@
       <c r="E27">
         <v>36</v>
       </c>
-      <c r="G27">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F27">
+        <f t="shared" si="1"/>
+        <v>7.2111025509279782</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <f t="shared" si="2"/>
         <v>520</v>
@@ -14254,12 +14979,12 @@
       <c r="E28">
         <v>39</v>
       </c>
-      <c r="G28">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F28">
+        <f t="shared" si="1"/>
+        <v>4.358898943540674</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <f t="shared" si="2"/>
         <v>540</v>
@@ -14277,12 +15002,12 @@
       <c r="E29">
         <v>40</v>
       </c>
-      <c r="G29">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F29">
+        <f t="shared" si="1"/>
+        <v>4.5825756949558398</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <f t="shared" si="2"/>
         <v>560</v>
@@ -14300,12 +15025,12 @@
       <c r="E30">
         <v>38</v>
       </c>
-      <c r="G30">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F30">
+        <f t="shared" si="1"/>
+        <v>8.1445278152470735</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <f t="shared" si="2"/>
         <v>580</v>
@@ -14323,12 +15048,12 @@
       <c r="E31">
         <v>33</v>
       </c>
-      <c r="G31">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F31">
+        <f t="shared" si="1"/>
+        <v>5.6862407030773205</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <f t="shared" si="2"/>
         <v>600</v>
@@ -14346,12 +15071,12 @@
       <c r="E32">
         <v>28</v>
       </c>
-      <c r="G32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F32">
+        <f t="shared" si="1"/>
+        <v>3.7859388972001873</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <f t="shared" si="2"/>
         <v>620</v>
@@ -14369,12 +15094,12 @@
       <c r="E33">
         <v>20</v>
       </c>
-      <c r="G33">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F33">
+        <f t="shared" si="1"/>
+        <v>1.7320508075688772</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <f t="shared" si="2"/>
         <v>640</v>
@@ -14392,12 +15117,12 @@
       <c r="E34">
         <v>21</v>
       </c>
-      <c r="G34">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F34">
+        <f t="shared" si="1"/>
+        <v>1.1547005383792515</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <f t="shared" si="2"/>
         <v>660</v>
@@ -14415,12 +15140,12 @@
       <c r="E35">
         <v>18</v>
       </c>
-      <c r="G35">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <f t="shared" si="2"/>
         <v>680</v>
@@ -14438,12 +15163,12 @@
       <c r="E36">
         <v>17</v>
       </c>
-      <c r="G36">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F36">
+        <f t="shared" si="1"/>
+        <v>2.6457513110645907</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <f t="shared" si="2"/>
         <v>700</v>
@@ -14461,12 +15186,12 @@
       <c r="E37">
         <v>13</v>
       </c>
-      <c r="G37">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F37">
+        <f t="shared" si="1"/>
+        <v>3.0550504633038904</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <f t="shared" si="2"/>
         <v>720</v>
@@ -14484,12 +15209,12 @@
       <c r="E38">
         <v>9</v>
       </c>
-      <c r="G38">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F38">
+        <f t="shared" si="1"/>
+        <v>1.5275252316519499</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <f t="shared" si="2"/>
         <v>740</v>
@@ -14507,12 +15232,12 @@
       <c r="E39">
         <v>9</v>
       </c>
-      <c r="G39">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F39">
+        <f t="shared" si="1"/>
+        <v>3.4641016151377544</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <f t="shared" si="2"/>
         <v>760</v>
@@ -14530,12 +15255,12 @@
       <c r="E40">
         <v>9</v>
       </c>
-      <c r="G40">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F40">
+        <f t="shared" si="1"/>
+        <v>3.0550504633038926</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <f t="shared" si="2"/>
         <v>780</v>
@@ -14553,12 +15278,12 @@
       <c r="E41">
         <v>5</v>
       </c>
-      <c r="G41">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F41">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <f t="shared" si="2"/>
         <v>800</v>
@@ -14576,206 +15301,14 @@
       <c r="E42">
         <v>6</v>
       </c>
-      <c r="G42">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G44">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G45">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G46">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G48">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G49">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G50">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G51">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G52">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G53">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G54">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G55">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G56">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G57">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G58">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G59">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G60">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G62">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G63">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G64">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G65">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G66">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G67">
-        <f t="shared" ref="G67:G79" si="3">MOD(A67,50)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G68">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G69">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G70">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G71">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G72">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G73">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G74">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="F42">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G75">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="G67:G79" si="3">MOD(A75,50)</f>
         <v>0</v>
       </c>
     </row>
@@ -14805,7 +15338,7 @@
     </row>
     <row r="80" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G80">
-        <f t="shared" ref="G67:G80" si="4">MOD(E80,50)</f>
+        <f t="shared" ref="G80" si="4">MOD(E80,50)</f>
         <v>0</v>
       </c>
     </row>
